--- a/output/casestudy_20260812.xlsx
+++ b/output/casestudy_20260812.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>6.449384199997439</v>
+        <v>6.334465299998556</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>6.617784300000494</v>
+        <v>5.873296500001743</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.67586460000166</v>
+        <v>5.935332600001857</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>6.367622300000221</v>
+        <v>5.986957000000984</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>6.531657100000302</v>
+        <v>5.918483199999173</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.653233299999556</v>
+        <v>6.06397189999916</v>
       </c>
     </row>
   </sheetData>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6.4 초</t>
+          <t>6.3 초</t>
         </is>
       </c>
     </row>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6.6 초</t>
+          <t>5.9 초</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.7 초</t>
+          <t>5.9 초</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.4 초</t>
+          <t>6.0 초</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.5 초</t>
+          <t>5.9 초</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.7 초</t>
+          <t>6.1 초</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>40.8 초</t>
+          <t>37.4 초</t>
         </is>
       </c>
     </row>
